--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7186,7 +7186,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7237,7 +7236,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7288,7 +7286,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7307,6 +7304,159 @@
       <c r="K129" t="inlineStr">
         <is>
           <t>Pain Point - How to Break the Cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>why-worklife</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Strategic Planning Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Podcast Rec - Why Every Leader Should Listen to WorkLife</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>worklife-lessons</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Strategic Planning Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Podcast Rec - 5 Leadership Lessons from WorkLife</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>start-here-worklife</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Strategic Planning Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Podcast Rec - New to WorkLife? Start Here</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7336,7 +7336,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7387,7 +7386,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7438,7 +7436,6 @@
           <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Strategic Planning Facilitator | Author</t>
@@ -7457,6 +7454,171 @@
       <c r="K132" t="inlineStr">
         <is>
           <t>Podcast Rec - New to WorkLife? Start Here</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Working Genius: 6 Types That Energise or Drain You</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6-types-of-working-genius</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>8</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>working-genius-6-types-2026-03-27/6-types-of-working-genius</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Working Genius: 6 Types That Energise or Drain You</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>why-your-team-feels-stuck</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>working-genius-6-types-2026-03-27/why-your-team-feels-stuck</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Working Genius: 6 Types That Energise or Drain You</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>genius-competency-frustration</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>8</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>working-genius-6-types-2026-03-27/genius-competency-frustration</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7622,6 +7622,171 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>The Five Dysfunctions of a Team (Summary)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>five-dysfunctions-overview</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>8</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>five-dysfunctions-team-2026-03-27/five-dysfunctions-overview</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>The Five Dysfunctions of a Team (Summary)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>signs-team-dysfunctional</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>8</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>five-dysfunctions-team-2026-03-27/signs-team-dysfunctional</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>The Five Dysfunctions of a Team (Summary)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>building-cohesive-team</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>8</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>five-dysfunctions-team-2026-03-27/building-cohesive-team</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7160,7 +7163,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>priorities-just-words</t>
+          <t>why-priorities-fail</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7170,7 +7173,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://consultclarity.org/post/every-year-we-set-priorities-and-do-the-same-things</t>
+          <t>N/A - Pain Point</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -7178,17 +7181,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/priorities-same-things</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/why-priorities-fail</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7198,19 +7206,19 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Pain Point - 5 Signs Your Priorities Are Just Words</t>
+          <t>Pain point topic, no people to tag</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>why-teams-repeat</t>
+          <t>signs-plan-will-fail</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7220,25 +7228,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://consultclarity.org/post/every-year-we-set-priorities-and-do-the-same-things</t>
+          <t>N/A - Pain Point</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/priorities-same-things</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/signs-plan-will-fail</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7248,12 +7261,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Pain Point - Why Teams Keep Doing the Same Things</t>
+          <t>Pain point topic, no people to tag</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7283,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://consultclarity.org/post/every-year-we-set-priorities-and-do-the-same-things</t>
+          <t>N/A - Pain Point</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -7278,17 +7291,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/priorities-same-things</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/break-the-cycle</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>IG, GBP, TikTok, YT (LI/FB/Threads/X/Bluesky failed)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>LI, FB, Threads, X, Bluesky</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7298,19 +7316,19 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Pain Point - How to Break the Cycle</t>
+          <t>Pain point topic, no people to tag</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>why-worklife</t>
+          <t>worklife-podcast-rec</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7320,7 +7338,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -7328,17 +7346,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-podcast-rec</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7353,14 +7371,14 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Podcast Rec - Why Every Leader Should Listen to WorkLife</t>
+          <t>All 9 platforms scheduled. @adamgrant tagged on Instagram.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>worklife-lessons</t>
+          <t>worklife-why-listen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7370,25 +7388,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-why-listen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7403,24 +7421,19 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Podcast Rec - 5 Leadership Lessons from WorkLife</t>
+          <t>All 9 platforms scheduled. 5 Reasons Leaders Should Listen theme.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>start-here-worklife</t>
+          <t>keynote-speaking-service</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>https://consultclarity.org/post/podcast-rec-worklife-adam-grant</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -7428,17 +7441,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousel-output/worklife-adam-grant</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/keynote-speaking-service</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Strategic Planning Facilitator | Author</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7453,337 +7466,1282 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Podcast Rec - New to WorkLife? Start Here</t>
+          <t>6 keynote topics overview. All 9 platforms.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>why-book-jonno</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Working Genius: 6 Types That Energise or Drain You</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Framework</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>6-types-of-working-genius</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>8</v>
+      <c r="D133" t="n">
+        <v>7</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/why-book-jonno</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>working-genius-6-types-2026-03-27/6-types-of-working-genius</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>5 reasons to book Jonno. All 9 platforms.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>exec-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Working Genius: 6 Types That Energise or Drain You</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Framework</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>why-your-team-feels-stuck</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>8</v>
+      <c r="D134" t="n">
+        <v>9</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/exec-team-dysfunction</t>
+        </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>working-genius-6-types-2026-03-27/why-your-team-feels-stuck</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>7 signs of dysfunction. Lencioni framework. All 9 platforms.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>fix-dysfunctional-team</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Working Genius: 6 Types That Energise or Drain You</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Framework</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>genius-competency-frustration</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>8</v>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/fix-dysfunctional-team</t>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Founder, Clarity Group Global</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>working-genius-6-types-2026-03-27/genius-competency-frustration</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>5 steps to high performance. Lencioni framework. All 9 platforms.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>asba-93-percent-proof</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>The Five Dysfunctions of a Team (Summary)</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>five-dysfunctions-overview</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
+      <c r="D136" t="n">
         <v>8</v>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-93-percent-proof-2026-03-27</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>YouTube (disconnected), Google Business (disconnected)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>five-dysfunctions-team-2026-03-27/five-dysfunctions-overview</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Stats/proof topic about ASBA 2025 conference results</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>asba-what-makes-pd-great</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>The Five Dysfunctions of a Team (Summary)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>signs-team-dysfunctional</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
+      <c r="D137" t="n">
         <v>8</v>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-what-makes-pd-great-2026-03-27</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>YouTube (disconnected), Google Business (disconnected)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>five-dysfunctions-team-2026-03-27/signs-team-dysfunctional</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>5 reasons Working Genius PD stands out</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>extreme-ownership-why-read</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>The Five Dysfunctions of a Team (Summary)</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Blog</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>building-cohesive-team</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
+      <c r="D138" t="n">
         <v>8</v>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-why-read-2026-03-27</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Why read Extreme Ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>extreme-ownership-principles</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-principles-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>5 key principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>extreme-ownership-apply</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>7</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-apply-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>How to apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>perfect-meeting-danger</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-danger-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>perfect-meeting-fix</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-fix-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>learning-leader-rec</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-rec-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Podcast recommendation overview, tags @ryanhawk12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>learning-leader-lessons</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-lessons-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>5 leadership lessons from the show, tags @ryanhawk12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>offsite-insights-edward-amey</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D145" t="n">
+        <v>8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>leadership-disability-edward-amey</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D146" t="n">
+        <v>7</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>why-leaders-need-a-coach</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>what-coaching-looks-like</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cost-of-no-coach</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>wg-6-types</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-6-types</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Working Genius: 6 Types Explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>wg-genius-or-frustration</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-genius-or-frustration</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Genius, Competency, or Frustration</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>wg-transforms-teams</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-transforms-teams</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>How Working Genius Transforms Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5d-overview</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overview</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Five Dysfunctions Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>5d-overcome</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overcome</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>How to Overcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>5d-warning-signs</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-warning-signs</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Warning Signs</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>crucial-conversations-overview</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Crucial Conversations by Patterson et al</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Book Rec</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>6</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>square, portrait, vertical</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>five-dysfunctions-team-2026-03-27/building-cohesive-team</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Book overview, 3 defining elements, pool of shared meaning, conditions for dialogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>crucial-conversations-state-method</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Crucial Conversations by Patterson et al</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Book Rec</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>7</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>STATE method: Share facts, Tell story, Ask others paths, Talk tentatively, Encourage testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>crucial-conversations-crib-technique</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Crucial Conversations by Patterson et al</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Book Rec</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>7</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>CRIB technique: Commit, Recognize, Invent, Brainstorm for finding mutual purpose</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8745,6 +8745,126 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>best-teacher-resigned-warning-signs</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Your Best Teacher Just Resigned</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pain Point</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>6</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>5 warning signs you missed, 75% stat, stay conversation advice</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>best-teacher-resigned-why-they-leave</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Your Best Teacher Just Resigned</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Pain Point</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Real reasons: invisible, bureaucracy, no voice, toxic culture, no future. $10-20K cost per teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>best-teacher-resigned-how-to-keep</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Your Best Teacher Just Resigned</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Pain Point</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>7</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>square, portrait, vertical</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>6 strategies: relationships, voice, growth, protect time. 2/3 nobody asked them to stay</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8628,240 +8628,915 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>crucial-conversations-overview</t>
+          <t>crucial-conversations-why-read</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Crucial Conversations by Patterson et al</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Book Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-why-read</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Book overview, 3 defining elements, pool of shared meaning, conditions for dialogue</t>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>crucial-conversations-state-method</t>
+          <t>crucial-conversations-7-skills</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Crucial Conversations by Patterson et al</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Book Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-7-skills</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>STATE method: Share facts, Tell story, Ask others paths, Talk tentatively, Encourage testing</t>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>crucial-conversations-crib-technique</t>
+          <t>crucial-conversations-apply</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Crucial Conversations by Patterson et al</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Book Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-apply</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>CRIB technique: Commit, Recognize, Invent, Brainstorm for finding mutual purpose</t>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>best-teacher-resigned-warning-signs</t>
+          <t>teacher-resigned-what-happened</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Your Best Teacher Just Resigned</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Pain Point</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-what-happened</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>5 warning signs you missed, 75% stat, stay conversation advice</t>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>best-teacher-resigned-why-they-leave</t>
+          <t>teacher-resigned-warning-signs</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Your Best Teacher Just Resigned</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Pain Point</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>square, portrait, vertical</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-warning-signs</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Real reasons: invisible, bureaucracy, no voice, toxic culture, no future. $10-20K cost per teacher</t>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>best-teacher-resigned-how-to-keep</t>
+          <t>teacher-resigned-how-to-keep</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Your Best Teacher Just Resigned</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Pain Point</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D161" t="n">
+        <v>8</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-how-to-keep</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>dare-to-lead-why-listen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>8</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-why-listen</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>dare-to-lead-key-themes</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
         <v>7</v>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>square, portrait, vertical</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-key-themes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>board-offsite-why</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, TikTok, Threads, YouTube, Google Business, X/Twitter, Bluesky</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>6 strategies: relationships, voice, growth, protect time. 2/3 nobody asked them to stay</t>
+      <c r="D164" t="n">
+        <v>8</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-why</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Service carousel for Board Offsite for Nonprofits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>board-offsite-5-signs</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>7</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-5-signs</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Service carousel for Board Offsite for Nonprofits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>The Pre-Brief Call</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>8</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/pre-brief-call</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Behind the scenes carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>5 Questions Before Every Offsite</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/5-questions-before-offsite</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Behind the scenes carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>What Is Vulnerability-Based Trust?</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>8</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/what-is-vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Concept overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7 Ways to Build Vulnerability-Based Trust</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>9</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/7-ways-vulnerability-trust</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Practical tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>The Leader Must Go First</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>8</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/leader-must-go-first</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Leadership role in trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Why Every Leader Should Read Atomic Habits</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>8</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/atomic-habits-book-rec</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Book rec carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>The 4 Laws of Behaviour Change</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>8</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/4-laws-behaviour-change</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Book rec carousel - framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>We Did an Offsite and Nothing Changed</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>8</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-nothing-changed-2026-03-27/offsite-nothing-changed</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Pain point carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>3 Signs Your Offsite Will Fail</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>7</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-nothing-changed-2026-03-27/3-signs-offsite-fail</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Pain point carousel - warning signs</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,12 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4928,40 +4925,35 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Why Listen to Craig Groeschel</t>
+          <t>school-pd-book-jonno</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>N/A - Podcast Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/why-listen</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-book-jonno-2026-03-27</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>X photo tags, YT @mentions</t>
+          <t>Instagram: verify tags</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4971,52 +4963,47 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Yes (pin created but Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
+          <t>School PD topic. ASBA 2025 stats.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5 Key Themes from Craig Groeschel</t>
+          <t>school-pd-great-day</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>N/A - Podcast Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/key-themes</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-great-day-2026-03-27</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>X photo tags, YT @mentions</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5026,52 +5013,47 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Yes (pin created but Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
+          <t>School PD topic. 6 steps for great PD.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3 Reasons to Subscribe</t>
+          <t>school-pd-reasons</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>N/A - Podcast Rec</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/reasons-subscribe</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-reasons-2026-03-27</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>X photo tags, YT @mentions</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5081,47 +5063,47 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Yes (pin created but Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
+          <t>School PD topic. 5 reasons to rethink PD.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>asba-working-genius-in-action</t>
+          <t>step-up-framework</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-working-genius-in-action-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-framework-2026-03-27</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5136,19 +5118,19 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
+          <t>3-stage Step Up or Step Out framework.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>asba-93-percent-rated-excellent</t>
+          <t>step-up-expectations</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -5156,22 +5138,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-93-percent-rated-excellent-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-expectations-2026-03-27</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5186,42 +5168,42 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
+          <t>Why clear expectations change everything.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>asba-what-school-leaders-took-away</t>
+          <t>personal-histories-exercise</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-what-school-leaders-took-away-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-exercise-2026-03-27</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
+          <t>Instagram: verify @patricklencioniofficial tag</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5236,32 +5218,27 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
+          <t>Lencioni Personal Histories Exercise. 3 questions.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>offsite-why-your-team-needs-one</t>
+          <t>personal-histories-why</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Service page: Leadership Team Offsite for Corporates</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-why-your-team-needs-one-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-why-2026-03-27</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5271,7 +5248,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>N/A - service post</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5286,29 +5263,24 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>N/A - no boards</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Service promotion carousel</t>
+          <t>Why every team should try Personal Histories.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>offsite-what-to-expect</t>
+          <t>ideal-team-player-why</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Service page: Leadership Team Offsite for Corporates</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -5316,7 +5288,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-what-to-expect-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-why-2026-03-27</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5326,7 +5298,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>N/A - service post</t>
+          <t>Instagram: verify @patricklencioniofficial tag</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5341,29 +5313,24 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>N/A - no boards</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Service promotion carousel</t>
+          <t>Humble Hungry Smart framework. Lencioni tagged.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>offsite-common-mistakes</t>
+          <t>ideal-team-player-missing</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Service page: Leadership Team Offsite for Corporates</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -5371,7 +5338,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-common-mistakes-2026-03-26</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-missing-2026-03-27</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5381,7 +5348,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>N/A - service post</t>
+          <t>Instagram: verify @patricklencioniofficial tag</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5396,4147 +5363,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>N/A - no boards</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Service promotion carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>offsite-book-your-offsite</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Service page: Leadership Team Offsite for Corporates</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>7</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-book-your-offsite-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>N/A - service post</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>N/A - no boards</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Service promotion carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>5-dysfunctions-overview</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>N/A (Framework topic)</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>9</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Framework explainer carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>5-dysfunctions-trust-conflict</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>N/A (Framework topic)</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Framework explainer carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>5-dysfunctions-commitment-results</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>N/A (Framework topic)</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>9</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Framework explainer carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>5-dysfunctions-action-plan</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>N/A (Framework topic)</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Framework explainer carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>imposter-syndrome-signs</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>N/A (Blog topic)</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Blog topic carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>imposter-syndrome-cost</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>N/A (Blog topic)</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Blog topic carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>imposter-syndrome-overcome</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>N/A (Blog topic)</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Blog topic carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>unreasonable-hospitality-why-read</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>7</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Book rec carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>unreasonable-hospitality-lessons</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>7</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Book rec carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>unreasonable-hospitality-apply</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>7</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Book rec carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>losing-teachers-warning-signs</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>N/A (Pain Point)</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Pain point carousel - school topic</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>losing-teachers-real-reasons</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>N/A (Pain Point)</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Pain point carousel - school topic</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>losing-teachers-what-to-do</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>N/A (Pain Point)</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>7</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Pain point carousel - school topic</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>hbr-ideacast-why-listen</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Podcast rec: HBR IdeaCast</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>hbr-ideacast-key-themes</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>7</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Podcast rec: HBR IdeaCast</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>hbr-ideacast-reasons-subscribe</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>6</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Podcast rec: HBR IdeaCast</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>redlands-wg-overview</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Testimonial: Michael Quach, Redlands College</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>7</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>redlands-wg-discoveries</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Testimonial: Michael Quach, Redlands College</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>7</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>redlands-wg-book-session</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Testimonial: Michael Quach, Redlands College</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>6</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>schools-wg-why</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Service: Working Genius Workshop for Schools</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>7</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>schools-wg-how</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Service: Working Genius Workshop for Schools</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>6</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>schools-wg-transform</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Service: Working Genius Workshop for Schools</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>6</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>wg-session-inside</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>What Actually Happens in a Working Genius Session</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>7</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>wg-session-moments</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>What Actually Happens in a Working Genius Session</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>7</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>wg-session-book</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>What Actually Happens in a Working Genius Session</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>5</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>understanding-uncertainty</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>8</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/understanding-uncertainty</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>decision-making-uncertainty</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>8</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/decision-making-uncertainty</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>communication-trust-uncertainty</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>8</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/communication-trust-uncertainty</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>resilience-adaptive-strategy</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>8</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/resilience-adaptive-strategy</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>radical-candor-why-read</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>8</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-why-read</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>radical-candor-four-quadrants</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>8</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-four-quadrants</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>radical-candor-in-practice</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>N/A (Book Rec)</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>8</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-in-practice</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>All platforms scheduled</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>why-priorities-fail</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>N/A - Pain Point</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>8</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/why-priorities-fail</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Pain point topic, no people to tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>signs-plan-will-fail</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>N/A - Pain Point</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>7</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/signs-plan-will-fail</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Pain point topic, no people to tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>break-the-cycle</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>N/A - Pain Point</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>8</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/break-the-cycle</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>IG, GBP, TikTok, YT (LI/FB/Threads/X/Bluesky failed)</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>LI, FB, Threads, X, Bluesky</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Pain point topic, no people to tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>worklife-podcast-rec</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>8</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-podcast-rec</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>All 9 platforms scheduled. @adamgrant tagged on Instagram.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>worklife-why-listen</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>7</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-why-listen</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>All 9 platforms scheduled. 5 Reasons Leaders Should Listen theme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>keynote-speaking-service</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>8</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/keynote-speaking-service</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>6 keynote topics overview. All 9 platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>why-book-jonno</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>7</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/why-book-jonno</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>5 reasons to book Jonno. All 9 platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>exec-team-dysfunction</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>9</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/exec-team-dysfunction</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>7 signs of dysfunction. Lencioni framework. All 9 platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>fix-dysfunctional-team</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>7</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/fix-dysfunctional-team</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Founder, Clarity Group Global</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>5 steps to high performance. Lencioni framework. All 9 platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>asba-93-percent-proof</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>8</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-93-percent-proof-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>YouTube (disconnected), Google Business (disconnected)</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Stats/proof topic about ASBA 2025 conference results</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>asba-what-makes-pd-great</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>8</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-what-makes-pd-great-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>YouTube (disconnected), Google Business (disconnected)</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>5 reasons Working Genius PD stands out</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>extreme-ownership-why-read</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>8</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-why-read-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>YouTube,GBP (disconnected)</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Why read Extreme Ownership</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>extreme-ownership-principles</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>8</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-principles-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>YouTube,GBP (disconnected)</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>5 key principles</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>extreme-ownership-apply</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>7</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-apply-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>YouTube,GBP (disconnected)</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>How to apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>perfect-meeting-danger</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>8</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-danger-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>YouTube, Google Business</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Pain point topic, no people to tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>perfect-meeting-fix</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>8</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-fix-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>YouTube, Google Business</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Pain point topic, no people to tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>learning-leader-rec</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>8</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-rec-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>YouTube, Google Business</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Podcast recommendation overview, tags @ryanhawk12</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>learning-leader-lessons</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>8</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-lessons-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>YouTube, Google Business</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>5 leadership lessons from the show, tags @ryanhawk12</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>offsite-insights-edward-amey</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D145" t="n">
-        <v>8</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>leadership-disability-edward-amey</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D146" t="n">
-        <v>7</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>why-leaders-need-a-coach</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D147" t="n">
-        <v>8</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Leadership Coach | Author</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Service promo: Executive Coaching for Leaders</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>what-coaching-looks-like</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D148" t="n">
-        <v>8</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Leadership Coach | Author</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Service promo: Executive Coaching for Leaders</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>cost-of-no-coach</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="D149" t="n">
-        <v>8</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Leadership Coach | Author</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Service promo: Executive Coaching for Leaders</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>wg-6-types</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>N/A - Framework topic</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>8</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-6-types</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Working Genius: 6 Types Explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>wg-genius-or-frustration</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>N/A - Framework topic</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>8</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-genius-or-frustration</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Genius, Competency, or Frustration</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>wg-transforms-teams</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>N/A - Framework topic</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>8</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-transforms-teams</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>How Working Genius Transforms Teams</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>5d-overview</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>N/A - Book summary</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>8</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overview</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>All 9 platforms</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Five Dysfunctions Overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>5d-overcome</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>N/A - Book summary</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>8</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overcome</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>All 9 platforms</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>How to Overcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>5d-warning-signs</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>N/A - Book summary</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>8</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-warning-signs</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>All 9 platforms</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Warning Signs</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>crucial-conversations-why-read</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>8</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-why-read</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Book rec carousel. No people tagged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>crucial-conversations-7-skills</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>9</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-7-skills</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Book rec carousel. No people tagged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>crucial-conversations-apply</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>8</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-apply</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Book rec carousel. No people tagged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>teacher-resigned-what-happened</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>8</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-what-happened</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Pain point carousel about teacher retention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>teacher-resigned-warning-signs</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>8</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-warning-signs</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Pain point carousel about teacher retention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>teacher-resigned-how-to-keep</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>8</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-how-to-keep</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Certified Working Genius Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Pain point carousel about teacher retention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>dare-to-lead-why-listen</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>8</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-why-listen</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>dare-to-lead-key-themes</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>7</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-key-themes</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>board-offsite-why</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>8</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-why</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Service carousel for Board Offsite for Nonprofits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>board-offsite-5-signs</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>7</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-5-signs</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Author</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Service carousel for Board Offsite for Nonprofits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>The Pre-Brief Call</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>8</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/pre-brief-call</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Behind the scenes carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>5 Questions Before Every Offsite</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>8</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/5-questions-before-offsite</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Behind the scenes carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>What Is Vulnerability-Based Trust?</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>8</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/what-is-vulnerability-based-trust</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Concept overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>7 Ways to Build Vulnerability-Based Trust</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>9</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/7-ways-vulnerability-trust</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Practical tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>The Leader Must Go First</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>8</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/leader-must-go-first</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Leadership role in trust</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Why Every Leader Should Read Atomic Habits</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>8</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/atomic-habits-book-rec</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Book rec carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>The 4 Laws of Behaviour Change</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>8</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/4-laws-behaviour-change</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Author | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Book rec carousel - framework</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>We Did an Offsite and Nothing Changed</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>8</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-nothing-changed-2026-03-27/offsite-nothing-changed</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Pain point carousel</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>3 Signs Your Offsite Will Fail</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>7</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-nothing-changed-2026-03-27/3-signs-offsite-fail</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Leadership Team Facilitator | Keynote Speaker</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Pain point carousel - warning signs</t>
+          <t>Missing virtues guide. Mess-Maker, Slacker, Politician.</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4925,35 +4928,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>school-pd-book-jonno</t>
+          <t>Why Listen to Craig Groeschel</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>N/A - Podcast Rec</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-book-jonno-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/why-listen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Instagram: verify tags</t>
+          <t>X photo tags, YT @mentions</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4963,47 +4971,52 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (pin created but Pinterest skipped)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>School PD topic. ASBA 2025 stats.</t>
+          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>school-pd-great-day</t>
+          <t>5 Key Themes from Craig Groeschel</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>N/A - Podcast Rec</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-great-day-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/key-themes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>X photo tags, YT @mentions</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5013,47 +5026,52 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (pin created but Pinterest skipped)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>School PD topic. 6 steps for great PD.</t>
+          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>school-pd-reasons</t>
+          <t>3 Reasons to Subscribe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>N/A - Podcast Rec</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-reasons-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/craig-groeschel-podcast-2026-03-26/reasons-subscribe</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>X photo tags, YT @mentions</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Certified Working Genius Facilitator | Author</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5063,47 +5081,47 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (pin created but Pinterest skipped)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>School PD topic. 5 reasons to rethink PD.</t>
+          <t>Pinterest skipped. TikTok scheduled Mar 31.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>step-up-framework</t>
+          <t>asba-working-genius-in-action</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-framework-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-working-genius-in-action-2026-03-26</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5118,19 +5136,19 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>3-stage Step Up or Step Out framework.</t>
+          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>step-up-expectations</t>
+          <t>asba-93-percent-rated-excellent</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -5138,22 +5156,22 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-expectations-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-93-percent-rated-excellent-2026-03-26</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5168,42 +5186,42 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Why clear expectations change everything.</t>
+          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>personal-histories-exercise</t>
+          <t>asba-what-school-leaders-took-away</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-exercise-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-what-school-leaders-took-away-2026-03-26</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Instagram: verify @patricklencioniofficial tag</t>
+          <t>TikTok (daily limit), YouTube (daily limit), Pinterest (no boards)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Certified Working Genius Facilitator | Author</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5218,27 +5236,32 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Lencioni Personal Histories Exercise. 3 questions.</t>
+          <t>ASBA 2025 testimonial carousel. TikTok/YouTube hit Buffer daily creation limits.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>personal-histories-why</t>
+          <t>offsite-why-your-team-needs-one</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Service page: Leadership Team Offsite for Corporates</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-why-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-why-your-team-needs-one-2026-03-26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5248,7 +5271,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>N/A - service post</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5263,24 +5286,29 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A - no boards</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Why every team should try Personal Histories.</t>
+          <t>Service promotion carousel</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ideal-team-player-why</t>
+          <t>offsite-what-to-expect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Service page: Leadership Team Offsite for Corporates</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -5288,7 +5316,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-why-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-what-to-expect-2026-03-26</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5298,7 +5326,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Instagram: verify @patricklencioniofficial tag</t>
+          <t>N/A - service post</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5313,24 +5341,29 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A - no boards</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Humble Hungry Smart framework. Lencioni tagged.</t>
+          <t>Service promotion carousel</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ideal-team-player-missing</t>
+          <t>offsite-common-mistakes</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Service page: Leadership Team Offsite for Corporates</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -5338,7 +5371,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-missing-2026-03-27</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-common-mistakes-2026-03-26</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5348,7 +5381,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Instagram: verify @patricklencioniofficial tag</t>
+          <t>N/A - service post</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5363,12 +5396,5512 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A - no boards</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Missing virtues guide. Mess-Maker, Slacker, Politician.</t>
+          <t>Service promotion carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>offsite-book-your-offsite</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Service page: Leadership Team Offsite for Corporates</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>7</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-book-your-offsite-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/A - service post</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>N/A - no boards</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Service promotion carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5-dysfunctions-overview</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>N/A (Framework topic)</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>9</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Framework explainer carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>5-dysfunctions-trust-conflict</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>N/A (Framework topic)</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Framework explainer carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>5-dysfunctions-commitment-results</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>N/A (Framework topic)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>9</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Framework explainer carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5-dysfunctions-action-plan</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>N/A (Framework topic)</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Framework explainer carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>imposter-syndrome-signs</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>N/A (Blog topic)</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Blog topic carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>imposter-syndrome-cost</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>N/A (Blog topic)</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Blog topic carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>imposter-syndrome-overcome</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>N/A (Blog topic)</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/imposter-syndrome-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Blog topic carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>unreasonable-hospitality-why-read</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>7</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Book rec carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>unreasonable-hospitality-lessons</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Book rec carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>unreasonable-hospitality-apply</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/unreasonable-hospitality-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Book rec carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>losing-teachers-warning-signs</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>N/A (Pain Point)</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Pain point carousel - school topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>losing-teachers-real-reasons</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>N/A (Pain Point)</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Pain point carousel - school topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>losing-teachers-what-to-do</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>N/A (Pain Point)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>7</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/losing-good-teachers-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Pain point carousel - school topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>hbr-ideacast-why-listen</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Podcast rec: HBR IdeaCast</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>hbr-ideacast-key-themes</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Podcast rec: HBR IdeaCast</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>hbr-ideacast-reasons-subscribe</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>6</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hbr-ideacast-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Podcast rec: HBR IdeaCast</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>redlands-wg-overview</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Testimonial: Michael Quach, Redlands College</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>redlands-wg-discoveries</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Testimonial: Michael Quach, Redlands College</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>redlands-wg-book-session</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Testimonial: Michael Quach, Redlands College</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/redlands-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Actual testimonial quote not found online - built around verified Redlands College engagement facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>schools-wg-why</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Service: Working Genius Workshop for Schools</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>schools-wg-how</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Service: Working Genius Workshop for Schools</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>schools-wg-transform</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Service: Working Genius Workshop for Schools</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>6</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/schools-working-genius-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>wg-session-inside</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>What Actually Happens in a Working Genius Session</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>wg-session-moments</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>What Actually Happens in a Working Genius Session</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>7</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>wg-session-book</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>What Actually Happens in a Working Genius Session</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/wg-session-inside-2026-03-26</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>understanding-uncertainty</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/understanding-uncertainty</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>decision-making-uncertainty</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/decision-making-uncertainty</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>communication-trust-uncertainty</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/communication-trust-uncertainty</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>resilience-adaptive-strategy</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/leading-through-uncertainty</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/leading-through-uncertainty-2026-03-26/resilience-adaptive-strategy</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>radical-candor-why-read</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-why-read</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>radical-candor-four-quadrants</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-four-quadrants</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>radical-candor-in-practice</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>N/A (Book Rec)</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/radical-candor-2026-03-26/radical-candor-in-practice</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>All platforms scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>why-priorities-fail</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>N/A - Pain Point</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/why-priorities-fail</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>signs-plan-will-fail</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>N/A - Pain Point</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>7</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/signs-plan-will-fail</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>LI, FB, IG, Threads, X, GBP, TikTok, YT, Bluesky</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>break-the-cycle</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>N/A - Pain Point</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/priorities-same-things-2026-03-26/break-the-cycle</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>IG, GBP, TikTok, YT (LI/FB/Threads/X/Bluesky failed)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>LI, FB, Threads, X, Bluesky</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>worklife-podcast-rec</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-podcast-rec</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>All 9 platforms scheduled. @adamgrant tagged on Instagram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>worklife-why-listen</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://www.yourthoughtpartner.com/blog/worklife-with-adam-grant-podcast</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/worklife-adam-grant-2026-03-26/worklife-why-listen</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>All 9 platforms scheduled. 5 Reasons Leaders Should Listen theme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>keynote-speaking-service</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/keynote-speaking-service</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>6 keynote topics overview. All 9 platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>why-book-jonno</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>7</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/keynote-speaking-2026-03-26/why-book-jonno</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>5 reasons to book Jonno. All 9 platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>exec-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>9</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/exec-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>7 signs of dysfunction. Lencioni framework. All 9 platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>fix-dysfunctional-team</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/exec-team-dysfunction-2026-03-26/fix-dysfunctional-team</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Founder, Clarity Group Global</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>5 steps to high performance. Lencioni framework. All 9 platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>asba-93-percent-proof</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-93-percent-proof-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>YouTube (disconnected), Google Business (disconnected)</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Stats/proof topic about ASBA 2025 conference results</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>asba-what-makes-pd-great</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/asba-what-makes-pd-great-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>YouTube (disconnected), Google Business (disconnected)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>5 reasons Working Genius PD stands out</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>extreme-ownership-why-read</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-why-read-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Why read Extreme Ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>extreme-ownership-principles</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-principles-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>5 key principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>extreme-ownership-apply</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>7</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/extreme-ownership-apply-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,Bluesky,TikTok</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>YouTube,GBP (disconnected)</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>How to apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>perfect-meeting-danger</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-danger-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>perfect-meeting-fix</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/perfect-meeting-fix-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Pain point topic, no people to tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>learning-leader-rec</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-rec-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Podcast recommendation overview, tags @ryanhawk12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>learning-leader-lessons</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/learning-leader-lessons-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Bluesky, TikTok</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>YouTube, Google Business</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>5 leadership lessons from the show, tags @ryanhawk12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>offsite-insights-edward-amey</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D145" t="n">
+        <v>8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>leadership-disability-edward-amey</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D146" t="n">
+        <v>7</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/testimonial-edward-amey-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Testimonial topic. Content from EP225 podcast and public bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>why-leaders-need-a-coach</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D147" t="n">
+        <v>8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>what-coaching-looks-like</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D148" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cost-of-no-coach</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/service-executive-coaching-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Leadership Coach | Author</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Service promo: Executive Coaching for Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>wg-6-types</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-6-types</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Working Genius: 6 Types Explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>wg-genius-or-frustration</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-genius-or-frustration</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Genius, Competency, or Frustration</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>wg-transforms-teams</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>N/A - Framework topic</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/working-genius-6-types-2026-03-27/wg-transforms-teams</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>How Working Genius Transforms Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>5d-overview</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overview</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Five Dysfunctions Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>5d-overcome</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-overcome</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>How to Overcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>5d-warning-signs</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>N/A - Book summary</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/five-dysfunctions-team-2026-03-27/5d-warning-signs</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>All 9 platforms</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Warning Signs</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>crucial-conversations-why-read</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>8</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-why-read</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>crucial-conversations-7-skills</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>9</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-7-skills</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>crucial-conversations-apply</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/crucial-conversations-book-rec-2026-03-27/crucial-conversations-apply</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Book rec carousel. No people tagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>teacher-resigned-what-happened</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-what-happened</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>teacher-resigned-warning-signs</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>8</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-warning-signs</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>teacher-resigned-how-to-keep</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>8</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/best-teacher-resigned-2026-03-27/teacher-resigned-how-to-keep</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Pain point carousel about teacher retention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>dare-to-lead-why-listen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>8</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-why-listen</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>dare-to-lead-key-themes</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>7</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/dare-to-lead-podcast-rec-2026-03-27/dare-to-lead-key-themes</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Podcast rec carousel for Dare to Lead with Brene Brown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>board-offsite-why</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>8</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-why</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Service carousel for Board Offsite for Nonprofits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>board-offsite-5-signs</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>7</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/board-offsite-nonprofits-2026-03-27/board-offsite-5-signs</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Service carousel for Board Offsite for Nonprofits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>The Pre-Brief Call</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>8</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/pre-brief-call</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Behind the scenes carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>5 Questions Before Every Offsite</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/pre-brief-zoom-call-2026-03-27/5-questions-before-offsite</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Behind the scenes carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>What Is Vulnerability-Based Trust?</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>8</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/what-is-vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Concept overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7 Ways to Build Vulnerability-Based Trust</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>9</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/7-ways-vulnerability-trust</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Practical tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>The Leader Must Go First</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/vulnerability-based-trust</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>8</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/vulnerability-based-trust-2026-03-27/leader-must-go-first</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Leadership role in trust</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Why Every Leader Should Read Atomic Habits</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>8</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/atomic-habits-book-rec</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Book rec carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>The 4 Laws of Behaviour Change</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>8</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/atomic-habits-2026-03-27/4-laws-behaviour-change</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Book rec carousel - framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>offsite-why-nothing-changed</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Pain Point: We Did an Offsite and Nothing Changed</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>8</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-pain-point-2026-03-27/offsite-why-nothing-changed</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>offsite-how-to-stick</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Pain Point: We Did an Offsite and Nothing Changed</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>8</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/offsite-pain-point-2026-03-27/offsite-how-to-stick</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>maxwell-podcast-why-listen</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>N/A (Podcast Rec)</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>8</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/maxwell-podcast-2026-03-27/maxwell-podcast-why-listen</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Podcast recommendation carousel - Why Listen</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>maxwell-podcast-key-themes</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>N/A (Podcast Rec)</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>8</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/maxwell-podcast-2026-03-27/maxwell-podcast-key-themes</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Podcast recommendation carousel - Key Themes</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>strategic-plan-why-facilitator</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>N/A (Service)</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>8</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/strategic-plan-2026-03-27/strategic-plan-why-facilitator</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Strategic Planning Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Service carousel - Why You Need a Facilitator</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>strategic-plan-5-signs-dust</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>N/A (Service)</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>8</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/strategic-plan-2026-03-27/strategic-plan-5-signs-dust</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Strategic Planning Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Service carousel - 5 Signs Plan Gathering Dust</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>step-up-10k-milestone</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>N/A (Stats and Proof)</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>8</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-10k-2026-03-27/step-up-10k-milestone</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>10,000+ Copies Sold milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>step-up-3-stages</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>N/A (Stats and Proof)</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>8</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-10k-2026-03-27/step-up-3-stages</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Pinterest (no boards)</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>3 Steps to Deal with Difficult People</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>build-relationships-first</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>N/A - researched topic</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>8</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/first-year-principal-2026-03-27/build-relationships-first</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Topic 1 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>avoid-common-mistakes</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>N/A - researched topic</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>8</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/first-year-principal-2026-03-27/avoid-common-mistakes</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Topic 1 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>lead-instruction-with-confidence</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>N/A - researched topic</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>8</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/first-year-principal-2026-03-27/lead-instruction-with-confidence</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Topic 1 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>why-read-hidden-potential</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>N/A - book rec</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>8</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hidden-potential-2026-03-27/why-read-hidden-potential</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Topic 2 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>key-ideas-hidden-potential</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>N/A - book rec</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>7</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hidden-potential-2026-03-27/key-ideas-hidden-potential</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Topic 2 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>apply-hidden-potential</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>N/A - book rec</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>7</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/hidden-potential-2026-03-27/apply-hidden-potential</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Topic 2 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>signs-of-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>N/A - pain point</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>9</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/talented-individually-dysfunctional-2026-03-27/signs-of-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Topic 3 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>root-causes-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>N/A - pain point</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>7</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/talented-individually-dysfunctional-2026-03-27/root-causes-team-dysfunction</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Topic 3 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>fix-dysfunctional-team</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>N/A - pain point</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>8</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/talented-individually-dysfunctional-2026-03-27/fix-dysfunctional-team</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Topic 3 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>why-listen-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>N/A - podcast rec</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>7</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/coaching-for-leaders-podcast-2026-03-27/why-listen-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Topic 4 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>best-episodes-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>N/A - podcast rec</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>8</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/coaching-for-leaders-podcast-2026-03-27/best-episodes-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Topic 4 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>lessons-from-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>N/A - podcast rec</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>7</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/coaching-for-leaders-podcast-2026-03-27/lessons-from-coaching-for-leaders</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, YouTube, Bluesky</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Topic 4 of 4 this session</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>school-pd-day-what-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/school-leadership-pd-day</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>8</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-day-what-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Topic 1A of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>school-pd-day-why-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/school-leadership-pd-day</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>8</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-day-why-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Certified Working Genius Facilitator | Author</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Topic 1B of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>step-up-framework-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/step-up-or-step-out-the-framework</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>8</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-framework-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Instagram, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>YouTube (queue full); LinkedIn, Facebook, Threads, X/Twitter (duplicate detected)</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Topic 2A - some platforms rejected as duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>step-up-signs-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/step-up-or-step-out-the-framework</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>7</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-signs-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Topic 2B of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>personal-histories-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/the-personal-histories-exercise</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>8</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Topic 3A of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>personal-histories-how-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/the-personal-histories-exercise</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>8</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-how-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Topic 3B of 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ideal-team-player-2026-03-27</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>https://www.consultclarity.org/post/the-ideal-team-player</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>9</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-2026-03-27</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>YouTube (queue full)</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Author | Keynote Speaker</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Yes (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Topic 4 of 4</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K199"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10523,7 +10523,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>school-pd-day-what-2026-03-27</t>
+          <t>school-pd-day-reasons</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10531,27 +10531,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/school-leadership-pd-day</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-day-what-2026-03-27</t>
+          <t>carousels/school-leadership-pd-day-2026-03-27/school-pd-day-reasons</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10566,19 +10562,19 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Topic 1A of 4</t>
+          <t>Service: School Leadership PD Day</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>school-pd-day-why-2026-03-27</t>
+          <t>school-pd-day-agenda</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10586,27 +10582,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/school-leadership-pd-day</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="n">
         <v>8</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-pd-day-why-2026-03-27</t>
+          <t>carousels/school-leadership-pd-day-2026-03-27/school-pd-day-agenda</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10621,19 +10613,19 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Topic 1B of 4</t>
+          <t>Service: School Leadership PD Day</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>step-up-framework-2026-03-27</t>
+          <t>step-up-framework</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10641,27 +10633,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/step-up-or-step-out-the-framework</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="n">
         <v>8</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-framework-2026-03-27</t>
+          <t>carousels/step-up-or-step-out-framework-2026-03-27/step-up-framework</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Instagram, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>YouTube (queue full); LinkedIn, Facebook, Threads, X/Twitter (duplicate detected)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -10676,19 +10664,19 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Topic 2A - some platforms rejected as duplicate</t>
+          <t>Framework: Step Up or Step Out</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>step-up-signs-2026-03-27</t>
+          <t>step-up-signs</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10696,27 +10684,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/step-up-or-step-out-the-framework</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="n">
         <v>7</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-signs-2026-03-27</t>
+          <t>carousels/step-up-or-step-out-framework-2026-03-27/step-up-signs</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -10731,19 +10715,19 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Topic 2B of 4</t>
+          <t>Framework: Step Up or Step Out</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>personal-histories-2026-03-27</t>
+          <t>personal-histories-what</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10751,27 +10735,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/the-personal-histories-exercise</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
         <v>8</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-2026-03-27</t>
+          <t>carousels/personal-histories-exercise-2026-03-27/personal-histories-what</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -10786,19 +10766,19 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Topic 3A of 4</t>
+          <t>Blog: The Personal Histories Exercise</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>personal-histories-how-2026-03-27</t>
+          <t>personal-histories-why</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10806,27 +10786,23 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/the-personal-histories-exercise</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-how-2026-03-27</t>
+          <t>carousels/personal-histories-exercise-2026-03-27/personal-histories-why</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -10841,19 +10817,19 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Topic 3B of 4</t>
+          <t>Blog: The Personal Histories Exercise</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ideal-team-player-2026-03-27</t>
+          <t>ideal-team-player-book</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10861,32 +10837,28 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>https://www.consultclarity.org/post/the-ideal-team-player</t>
-        </is>
-      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-2026-03-27</t>
+          <t>carousels/ideal-team-player-book-rec-2026-03-27/ideal-team-player-book</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, TikTok, Bluesky</t>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>YouTube (queue full)</t>
+          <t>IG tags, X tags</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Author | Keynote Speaker</t>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -10896,12 +10868,63 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Yes (Pinterest skipped)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Topic 4 of 4</t>
+          <t>Book Rec: The Ideal Team Player</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ideal-team-player-missing</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="n">
+        <v>8</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>carousels/ideal-team-player-book-rec-2026-03-27/ideal-team-player-missing</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>IG tags, X tags</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Book Rec: The Ideal Team Player</t>
         </is>
       </c>
     </row>

--- a/carousel-data/carousel-log.xlsx
+++ b/carousel-data/carousel-log.xlsx
@@ -10523,7 +10523,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>school-pd-day-reasons</t>
+          <t>what-a-pd-day-looks-like</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10531,23 +10531,27 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>N/A - service page</t>
+        </is>
+      </c>
       <c r="D193" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>carousels/school-leadership-pd-day-2026-03-27/school-pd-day-reasons</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-leadership-pd-day-2026-03-27/what-a-pd-day-looks-like</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10562,19 +10566,15 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Service: School Leadership PD Day</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>school-pd-day-agenda</t>
+          <t>why-book-jonno-pd-day</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10582,23 +10582,27 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>N/A - service page</t>
+        </is>
+      </c>
       <c r="D194" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>carousels/school-leadership-pd-day-2026-03-27/school-pd-day-agenda</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/school-leadership-pd-day-2026-03-27/why-book-jonno-pd-day</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10613,19 +10617,15 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Service: School Leadership PD Day</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>step-up-framework</t>
+          <t>step-up-step-out-framework</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -10633,28 +10633,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>N/A - framework</t>
+        </is>
+      </c>
       <c r="D195" t="n">
         <v>8</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>carousels/step-up-or-step-out-framework-2026-03-27/step-up-framework</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-step-out-2026-03-27/step-up-step-out-framework</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Author | Keynote Speaker</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -10664,19 +10668,15 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Framework: Step Up or Step Out</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>step-up-signs</t>
+          <t>5-signs-have-conversation</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10684,28 +10684,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>N/A - framework</t>
+        </is>
+      </c>
       <c r="D196" t="n">
         <v>7</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>carousels/step-up-or-step-out-framework-2026-03-27/step-up-signs</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/step-up-step-out-2026-03-27/5-signs-have-conversation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Author | Keynote Speaker</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -10715,19 +10719,15 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Framework: Step Up or Step Out</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>personal-histories-what</t>
+          <t>build-trust-30-minutes</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10735,28 +10735,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>N/A - blog</t>
+        </is>
+      </c>
       <c r="D197" t="n">
         <v>8</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>carousels/personal-histories-exercise-2026-03-27/personal-histories-what</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-exercise-2026-03-27/build-trust-30-minutes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -10766,19 +10770,15 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Blog: The Personal Histories Exercise</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>personal-histories-why</t>
+          <t>how-to-run-personal-histories</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10786,28 +10786,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>N/A - blog</t>
+        </is>
+      </c>
       <c r="D198" t="n">
         <v>7</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>carousels/personal-histories-exercise-2026-03-27/personal-histories-why</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/personal-histories-exercise-2026-03-27/how-to-run-personal-histories</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -10817,14 +10821,10 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Blog: The Personal Histories Exercise</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10837,28 +10837,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>N/A - book rec</t>
+        </is>
+      </c>
       <c r="D199" t="n">
         <v>8</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>carousels/ideal-team-player-book-rec-2026-03-27/ideal-team-player-book</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-book-rec-2026-03-27/ideal-team-player-book</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -10868,19 +10872,15 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Book Rec: The Ideal Team Player</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ideal-team-player-missing</t>
+          <t>are-you-ideal-team-player</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10888,28 +10888,32 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>N/A - book rec</t>
+        </is>
+      </c>
       <c r="D200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>carousels/ideal-team-player-book-rec-2026-03-27/ideal-team-player-missing</t>
+          <t>https://github.com/jonno-alt/social-images/tree/main/carousels/ideal-team-player-book-rec-2026-03-27/are-you-ideal-team-player</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>LI,FB,IG,Threads,X,GBP,Bluesky,TikTok,YouTube</t>
+          <t>LinkedIn, Facebook, Instagram, Threads, X/Twitter, Google Business, Bluesky, TikTok, YouTube</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>IG tags, X tags</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Leadership Team Facilitator | Keynote Speaker | Author</t>
+          <t>Leadership Team Facilitator | Author</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10919,14 +10923,10 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Book Rec: The Ideal Team Player</t>
-        </is>
-      </c>
+          <t>No (Pinterest skipped)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
